--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_12_Full_159_Cau/Day_12_Ngan_Hang_Phan_07_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_12_Full_159_Cau/Day_12_Ngan_Hang_Phan_07_20_Cau.xlsx
@@ -624,10 +624,31 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: So sánh version của model, prompt và source trước khi xét độ tương đồng của query.
-Phân tích theo nguyên lý thiết kế: So sánh version của model, prompt và source trước khi xét độ tương đồng của query.</t>
+- [1.0 điểm] Phân loại chính xác CACHE MISS do sự thay đổi của Knowledge Source (v3 -&gt; v4) và Policy Prompt.
+- [1.5 điểm] Thiết lập cấu trúc khóa cache đa thành phần kết hợp: Model, Prompt Hash, Source Version và Query Embedding.
+- [1.5 điểm] Đưa ra quyết định vô hiệu hóa toàn diện bằng chiến lược Version-Based Namespacing và định tuyến gọi model mới.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân loại Hit / Miss Dựa trên Thứ bậc Khóa Đệm Ngữ nghĩa (Semantic Cache Key Hierarchy):
+   - Cấu trúc Khóa Đệm Hoàn chỉnh (Composite Cache Key Structure):
+     Khóa lưu trữ trong Semantic Cache phải được cấu thành từ 4 yếu tố bắt buộc:
+     `Cache_Key = Hash(Model_Identity, System_Prompt_Policy_Hash, Knowledge_Source_Version, Query_Embedding)`
+   - Đối chiếu với các điều kiện trong bối cảnh:
+     + Knowledge Source: Đã được nâng cấp từ phiên bản `v3` lên `v4` (Tri thức nền tảng đã thay đổi).
+     + Policy Prompt: Đã thay đổi nội dung (Chính sách an toàn, giọng điệu hoặc định dạng đầu ra mới).
+     + Query: Có ý nghĩa ngữ nghĩa gần giống với một bản ghi cũ đã lưu.
+   - Kết luận Phân loại: CACHE MISS (hoặc CACHE ENTRY BỊ VÔ HIỆU HÓA HOÀN TOÀN).
+     Lý do: Mặc dù vector ngữ nghĩa của câu hỏi có độ tương đồng cosine rất cao ($\ge 0.95$), nhưng việc Knowledge Source và Policy Prompt thay đổi đã làm gãy ranh giới hợp lệ của bản ghi cũ. Nếu trả về kết quả cũ, hệ thống sẽ cung cấp thông tin sai lệch, lỗi thời và vi phạm chính sách mới của doanh nghiệp.
+2. Quyết định Vô hiệu hóa và Chiến lược Thực thi (Invalidation Decision &amp; Execution):
+   - Quyết định: VÔ HIỆU HÓA TOÀN BỘ CÁC BẢN GHI ĐƯỢC TẠO DƯỚI SOURCE V3 VÀ PROMPT POLICY CŨ.
+   - Chiến lược Vô hiệu hóa Không gian Tên theo Phiên bản (Version-Based Namespacing Invalidation):
+     Thay vì phải duyệt tìm và xóa hàng triệu khóa tốn kém trong bộ nhớ, hệ thống chỉ cần cập nhật tiền tố không gian tên toàn cục (Global Cache Namespace):
+     `active_namespace = "prompt_v2:source_v4"`.
+     Mọi truy vấn mới sẽ tự động tra cứu trong namespace mới. Các bản ghi thuộc `source_v3` cũ sẽ tự động bị bỏ qua và được hệ thống dọn dẹp dần theo chính sách TTL tự nhiên.
+   - Luồng Thực thi Tiếp theo: Đưa yêu cầu tới Model Provider cùng tài liệu v4 và prompt policy mới, sau đó lưu kết quả phản hồi mới vào cache với khóa thuộc namespace v4.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Bộ nhớ đệm ngữ nghĩa (Semantic Caching) trong các ứng dụng AI đòi hỏi sự quản lý nghiêm ngặt về tính hợp lệ của tri thức. Độ tương đồng ngữ nghĩa của câu hỏi chỉ có giá trị khi ngữ cảnh tri thức nền tảng và chính sách vận hành được giữ nguyên. Việc vô hiệu hóa cache theo không gian tên phiên bản bảo đảm câu trả lời luôn cập nhật tri thức mới nhất mà không gây suy thoái hiệu năng tra cứu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+GPTCache Architectural Patterns: https://github.com/zilliztech/GPTCache và Redis Semantic Caching Best Practices</t>
         </is>
       </c>
     </row>
@@ -754,10 +775,32 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Theo dõi thời điểm slot A rảnh và thời điểm request C được nhận vào.
-Phân tích theo nguyên lý thiết kế: Theo dõi thời điểm slot A rảnh và thời điểm request C được nhận vào.</t>
+- [1.0 điểm] Phân tích chính xác hạn chế của Static Batching: Slot A bị bỏ trống 8 bước và C phải chờ hết bước 10 mới được vào (tổng 13 bước).
+- [1.5 điểm] Mô tả chính xác cơ chế Continuous Batching: C được nạp ngay vào slot của A ở bước 3, chạy song song với B và hoàn tất ở bước 5.
+- [1.5 điểm] So sánh định lượng thời gian: Continuous Batching chỉ tốn 10 bước (tiết kiệm 23% thời gian) và triệt tiêu GPU bubbles.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. So sánh Lịch Thực thi của Static Batching và Continuous Batching:
+   - Bối cảnh: Ba yêu cầu A, B, C có độ dài sinh token đầu ra lần lượt là: A cần 2 tokens, B cần 10 tokens, C cần 3 tokens. Giả sử ban đầu batch có 2 slots xử lý A và B. Slot của A rỗng sau bước giải mã thứ 2.
+   - Kịch bản 1: Gom cụm Tĩnh Truyền thống (Static Batching):
+     + Bước 1 - 2: A và B cùng chạy trong batch. Sau bước 2, Request A hoàn tất (đủ 2 tokens).
+     + Bước 3 - 10: Do Static Batching khóa cứng toàn bộ batch cho đến khi request dài nhất (B cần 10 tokens) kết thúc hoàn toàn, slot của A bị BỎ TRỐNG LÃNG PHÍ (Wasted Idle Bubble) suốt 8 bước tiếp theo.
+     + Request C (cần 3 tokens) BỊ BẮT BUỘC PHẢI CHỜ ĐỢI trong hàng đợi ngoài cho đến hết bước 10.
+     + Bước 11 - 13: Request C mới được đưa vào batch mới và chạy trong 3 bước.
+     + Tổng thời gian hoàn tất cả 3 requests: $10 \text{ bước (Batch 1)} + 3 \text{ bước (Batch 2)} = 13 \text{ bước giải mã (Decode Steps)}$.
+   - Kịch bản 2: Gom cụm Liên tục (Continuous Batching / Iteration-Level Scheduling):
+     + Bước 1 - 2: A và B cùng chạy trong batch.
+     + Bước 2: Request A hoàn tất. Hệ thống lập tức giải phóng (evict) A ra khỏi slot.
+     + Bước 3: Request C ĐƯỢC CHÈN NGAY VÀO SLOT RỖNG VỪA GIẢI PHÓNG ở cấp độ từng bước lặp (Iteration level). Slot không bị rảnh một giây nào.
+     + Bước 3 - 5: B và C chạy song song cùng nhau. Đến hết bước 5, Request C hoàn tất (đủ 3 tokens).
+     + Bước 6 - 10: Slot của C giải phóng, B tiếp tục chạy nốt 5 bước cuối cùng cho đến khi hoàn tất ở bước 10.
+     + Tổng thời gian hoàn tất cả 3 requests: CHỈ MẤT ĐÚNG 10 BƯỚC GIẢI MÃ.
+2. Đánh giá Hiệu năng và Tiết kiệm Tài nguyên:
+   - Continuous Batching tiết kiệm $13 - 10 = 3$ bước giải mã (giảm $\approx 23\%$ tổng thời gian thực thi).
+   - Triệt tiêu hoàn toàn hiện tượng bong bóng rỗi GPU (Zero GPU Idle Bubbles), tăng gấp đôi thông lượng phục vụ (Throughput) và giảm mạnh thời gian chờ đợi (Queue Wait Time) của Request C.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Kỹ thuật Continuous Batching (hay Iteration-Level Batching do vLLM và Orca tiên phong) đã thay đổi hoàn toàn cách thức phục vụ mô hình ngôn ngữ lớn. Bằng cách cho phép các yêu cầu mới gia nhập batch ngay khi có một yêu cầu khác hoàn tất ở cấp độ từng token lặp, hệ thống tối đa hóa mức độ sử dụng tính toán của GPU và loại bỏ hoàn toàn sự lãng phí tài nguyên do độ dài văn bản không đồng nhất.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Orca: A Distributed Serving System for Transformer-Based Generative Models (OSDI '22) &amp; vLLM Continuous Batching Architecture</t>
         </is>
       </c>
     </row>
@@ -836,10 +879,34 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tính số block cần cho một sequence trước, rồi nhân với năm.
-Phân tích theo nguyên lý thiết kế: Tính số block cần cho một sequence trước, rồi nhân với năm.</t>
+- [1.0 điểm] Tính toán chính xác mỗi sequence 17 tokens cần 2 blocks (32 slots) theo thuật toán PagedAttention.
+- [1.5 điểm] Tính toán chính xác 5 sequence chiếm trọn 10 blocks (160 slots), lấp đầy 100% ngân sách bộ nhớ GPU.
+- [1.5 điểm] Chỉ ra rõ ràng nghịch lý phân mảnh: chỉ có 85 tokens thực tế (53%) nhưng lãng phí 75 slots (47%), làm cạn kiệt năng lực nhận thêm request.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Số lượng Block và Slot Phân bổ theo Cơ chế PagedAttention:
+   - Thông số hệ thống:
+     + Ngân sách tối đa của GPU: $160$ KV token slots.
+     + Kích thước mỗi khối bộ nhớ (Block Size): $B = 16$ tokens/block.
+     + Tổng số block bộ nhớ vật lý trên GPU: $160 / 16 = 10$ physical blocks.
+     + Số lượng chuỗi cần phục vụ: $5$ sequences, mỗi chuỗi có độ dài $L = 17$ tokens.
+   - Tính toán Phân bổ Khối cho Một Chuỗi Đơn lẻ (Per-Sequence Allocation):
+     + Vì độ dài chuỗi là 17 tokens, vượt quá dung lượng 16 tokens của một block đơn lẻ, thuật toán quản lý bộ nhớ trang (PagedAttention) bắt buộc phải cấp phát 2 blocks nguyên vẹn:
+       $\text{Blocks required per sequence} = \lceil 17 / 16 \rceil = 2 \text{ blocks}$.
+     + Tổng số slots bị cấp phát cho 1 chuỗi: $2 \times 16 = 32$ slots.
+     + Phân tích lãng phí nội bộ (Internal Fragmentation): Trong 32 slots được cấp phát, có 17 slots chứa token thực tế, và có $32 - 17 = 15$ slots bị bỏ trống (lãng phí phân mảnh) trong block thứ hai.
+2. Đánh giá Ảnh hưởng Toàn cục Lên Năng lực Phục vụ của GPU (Capacity Impact):
+   - Tổng số block thực tế bị chiếm dụng bởi 5 chuỗi:
+     $5 \text{ sequences} \times 2 \text{ blocks} = 10 \text{ physical blocks}$.
+   - Tổng số slot bộ nhớ bị khóa chặt trên GPU:
+     $10 \text{ blocks} \times 16 \text{ slots/block} = 160 \text{ token slots}$.
+   - Đánh giá Năng lực Phục vụ Còn lại (Available Capacity):
+     $160 \text{ slots bị chiếm} / 160 \text{ slots ngân sách} = 100\%$ dung lượng bộ nhớ KV Cache ĐÃ BỊ LẤP ĐẦY HOÀN TOÀN (0 block và 0 slot trống còn lại).
+   - Kết luận Tác động Kỹ thuật:
+     Mặc dù tổng số token hữu ích thực tế chỉ là $5 \times 17 = 85$ tokens (chỉ chiếm $53.125\%$ tổng dung lượng vật lý), nhưng do hiện tượng phân mảnh khối nội bộ ($5 \times 15 = 75$ slots lãng phí, chiếm $46.875\%$ dung lượng), toàn bộ GPU đã bị cạn kiệt bộ nhớ. Hệ thống KHÔNG THỂ TIẾP NHẬN THÊM BẤT KỲ YÊU CẦU MỚI NÀO và sẽ xảy ra hiện tượng OOM hoặc bắt buộc phải kích hoạt cơ chế hoán đổi (Swapping/Preemption) nếu bất kỳ chuỗi nào sinh thêm token tiếp theo.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+PagedAttention (sử dụng trong vLLM) giải quyết triệt để sự phân mảnh bộ nhớ bên ngoài của KV Cache bằng cách phân bổ các block kích thước cố định. Tuy nhiên, sự phân mảnh bên trong (Internal Fragmentation) vẫn xảy ra khi chuỗi văn bản vượt qua ranh giới block một lượng token rất nhỏ. Hiểu rõ sự đánh đổi này giúp các kỹ sư điều chỉnh kích thước block size phù hợp với đặc thù độ dài dữ liệu của doanh nghiệp.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Efficient Memory Management for Large Language Model Serving with PagedAttention (vLLM Paper, SOSP '23)</t>
         </is>
       </c>
     </row>
@@ -918,10 +985,30 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: So sánh chi phí draft và kiểm chứng với số proposal thực sự được chấp nhận.
-Phân tích theo nguyên lý thiết kế: So sánh chi phí draft và kiểm chứng với số proposal thực sự được chấp nhận.</t>
+- [1.0 điểm] Trình bày chính xác điều kiện tiên quyết của Speculative Decoding: Draft model phải siêu nhanh và tỷ lệ chấp thuận phải cao.
+- [1.5 điểm] Phân tích khối lượng tính toán (Work/FLOPs): Tăng gấp gần 2 lần do phải chạy cả hai mô hình mà hầu hết token bị vứt bỏ.
+- [1.5 điểm] Chứng minh độ trễ (Latency) bị suy thoái (Negative Speedup) và đưa ra quyết định kiến trúc: Tắt ngay Speculative Decoding.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tích Nguyên lý Hoạt động của Suy luận Đầu cơ (Speculative Decoding Principles):
+   - Cơ chế cốt lõi: Một mô hình phác thảo nhỏ và siêu nhanh (Draft Model) sinh trước một chuỗi $K$ tokens giả định với chi phí thấp. Sau đó, mô hình mục tiêu lớn (Target Model) chỉ cần chạy đúng 1 lần tính toán song song (Forward Pass) để xác thực và chấp thuận hoặc bác bỏ các token đề xuất đó.
+   - Điều kiện Tiên quyết để Đạt Tăng tốc Hiệu quả (Speedup Conditions):
+     + Tốc độ sinh của Draft Model phải nhanh hơn Target Model rất nhiều lần ($T_{draft} \ll T_{target}$, thường nhanh hơn từ 5 đến 10 lần).
+     + Tỷ lệ Chấp thuận Token (Acceptance Rate $\alpha$) phải ở mức cao (thường $\alpha \ge 65-80\%$).
+2. So sánh Khối lượng Tính toán (Work) và Độ trễ (Latency) trong Điều kiện Đề bài:
+   - Bối cảnh đề bài: 'Draft model chậm gần bằng target ($T_{draft} \approx T_{target}$)' và 'Tỷ lệ proposal được chấp nhận rất thấp (ví dụ $\alpha \approx 10-20\%$)'.
+   - So sánh Khối lượng Công việc Tính toán (Computational Work / FLOPs):
+     Trong Speculative Decoding, hệ thống phải thực hiện tính toán trên CẢ HAI MÔ HÌNH: Chạy $K$ bước trên Draft Model, cộng thêm 1 lần chạy trên Target Model để kiểm chứng và sửa lỗi. Do phần lớn các token bị bác bỏ, tổng khối lượng tính toán (FLOPs) GẤP GẦN 2 LẦN so với phương pháp Decoding thông thường, gây lãng phí năng lượng và tài nguyên tính toán GPU cực lớn.
+   - So sánh Độ trễ Thực tế (Wall-Clock Latency):
+     Thời gian để sinh một số lượng token nhất định:
+     $T_{speculative} = K \times T_{draft} + T_{target\_verify} + T_{recovery}$.
+     Vì $T_{draft} \approx T_{target}$ và hầu hết các token đề xuất đều bị vứt bỏ, thời gian bỏ ra để sinh các token nháp bị lãng phí hoàn toàn mà Target Model vẫn phải tự sinh lại từ đầu. Kết quả: ĐỘ TRỄ CỦA SPECULATIVE DECODING CAO HƠN ĐÁNG KỂ SO VỚI DECODING THÔNG THƯỜNG ($T_{speculative} &gt; T_{standard}$).
+3. Kết luận và Khuyến nghị Kiến trúc:
+   - Trong điều kiện này, Speculative Decoding tạo ra 'Tăng tốc Âm' (Negative Speedup / Latency Penalty) và làm suy thoái nghiêm trọng hiệu năng hệ thống.
+   - Khuyến nghị: NGAY LẬP TỨC VÔ HIỆU HÓA (DISABLE) Speculative Decoding và quay trở lại phương thức Auto-Regressive Decoding thông thường của Target Model.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Suy luận đầu cơ (Speculative Decoding) không phải là chiếc đũa thần trong mọi trường hợp. Hiệu quả kinh tế và độ trễ của nó hoàn toàn phụ thuộc vào khoảng cách tốc độ giữa hai mô hình và độ chính xác của các đề xuất. Khi mô hình nháp quá nặng hoặc sinh sai quá nhiều, chi phí xác thực và khắc phục lỗi sẽ vượt quá lợi ích mang lại, biến tối ưu hóa thành gánh nặng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Fast Inference from Transformers via Speculative Decoding (Leviathan et al., ICML 2023) &amp; Google DeepMind Speculative Decoding Analysis</t>
         </is>
       </c>
     </row>
@@ -1000,10 +1087,31 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đặt độ dài output cạnh bottleneck decode và chi phí KV transfer trước khi chọn placement.
-Phân tích theo nguyên lý thiết kế: Đặt độ dài output cạnh bottleneck decode và chi phí KV transfer trước khi chọn placement.</t>
+- [1.0 điểm] Phân tích chính xác điểm nghẽn nằm ở giai đoạn Decode 5.000 tokens (Memory-bound) chứ không phải ở Prefill 20 tokens.
+- [1.5 điểm] So sánh chi phí đánh đổi: Thời gian truyền mạng KV 200ms lớn gấp 20-40 lần thời gian tính prefill (5-10ms) kèm rủi ro mạng chập chờn.
+- [1.5 điểm] Đưa ra quyết định chuẩn xác: Không phân tách (Do not disaggregate), giữ mô hình Co-located trên cùng một máy chủ GPU.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá Bản chất Khối lượng Công việc và Điểm nghẽn Cốt tử (Workload Bottleneck Analysis):
+   - Phân tích bối cảnh: Yêu cầu có prompt siêu ngắn là $20$ tokens nhưng sinh văn bản đầu ra siêu dài là $5.000$ tokens. Tỷ lệ giữa giai đoạn Prefill và giai đoạn Decode là $20 : 5000 = 1 : 250$.
+   - Xác định Điểm nghẽn (Primary Bottleneck):
+     + Giai đoạn Prefill (Compute-Bound): Chỉ mất $20$ tokens tính toán song song, hoàn tất trong vòng $5-10$ mili-giây trên bất kỳ GPU hiện đại nào.
+     + Giai đoạn Decode (Memory-Bound): Chiếm tới $99.8\%$ tổng thời gian thực thi của yêu cầu (thực hiện $5.000$ bước đọc tuần tự weights và KV Cache từ VRAM).
+     + Kết luận: Điểm nghẽn duy nhất của hệ thống nằm ở BĂNG THÔNG BỘ NHỚ VRAM CỦA PHA DECODE (Memory Bandwidth Bottleneck), hoàn toàn không có hiện tượng nghẽn tính toán ở pha Prefill.
+2. Đánh giá Mô hình Tách rời Prefill/Decode (Disaggregated Serving Evaluation):
+   - Kiến trúc Tách rời (Disaggregated Architecture): Tách riêng cụm Prefill Nodes chuyên tính prompt và chuyển giao dữ liệu KV Cache qua mạng nội bộ cho cụm Decode Nodes chuyên sinh token.
+   - Rủi ro Mạng trong Bối cảnh:
+     + Độ trễ truyền tải KV Cache qua mạng: $200$ms.
+     + Tình trạng mạng: 'Mạng không ổn định' (Network Jitter, Packet Drop, Unreliable Latency).
+   - So sánh Chi phí Đánh đổi:
+     Nếu tách rời, để tiết kiệm $5-10$ms tính toán prefill, hệ thống phải trả giá bằng $200$ms chờ truyền mạng (đắt gấp 20 đến 40 lần) cộng thêm rủi ro gãy kết nối mạng khiến request bị lỗi hoặc timeout.
+3. Quyết định Kiến trúc Bố trí Tài nguyên (Placement &amp; Disaggregation Decision):
+   - QUYẾT ĐỊNH DỨT KHOÁT: TUYỆT ĐỐI KHÔNG PHÂN TÁCH KIẾN TRÚC (DO NOT DISAGGREGATE).
+   - Bố trí Tối ưu: Áp dụng Mô hình Hợp nhất Đặt cùng Chỗ (Co-located Single-Node Placement).
+     Thực thi cả giai đoạn Prefill và toàn bộ 5.000 bước Decode trên cùng một Worker GPU / Node. Bằng cách này, KV cache được giữ nguyên trực tiếp trong bộ nhớ VRAM cục bộ với băng thông cực cao (hàng TB/s), triệt tiêu hoàn toàn 200ms độ trễ mạng và miễn nhiễm với sự thiếu ổn định của hạ tầng mạng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Kiến trúc phân tách Prefill/Decode chỉ mang lại hiệu quả khi khối lượng công việc có prompt cực dài (hàng nghìn đến hàng vạn tokens) và hạ tầng mạng sở hữu băng thông siêu cao (như InfiniBand/RoCE dưới 1ms). Khi prompt ngắn và mạng không ổn định, chi phí truyền tải mạng (Network Overhead) sẽ biến việc phân tách thành một thảm họa về độ trễ và độ tin cậy.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+DistServe: Disaggregating Prefill and Decoding for Goodput-optimized Large Language Model Serving (OSDI '24) &amp; vLLM Architecture Analysis</t>
         </is>
       </c>
     </row>
@@ -1086,10 +1194,28 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Phân biệt timeout trước connect với timeout sau khi request đã được gửi.
-Phân tích theo nguyên lý thiết kế: Phân biệt timeout trước connect với timeout sau khi request đã được gửi.</t>
+- [1.0 điểm] Phân loại chuẩn xác trạng thái hoàn tất cho cả 3 timeline: A chưa hoàn tất, B chắc chắn hoàn tất, C lơ lửng không rõ.
+- [1.5 điểm] Đánh giá retry safety cho Timeline A (an toàn tuyệt đối) và Timeline B (cấm retry thực thi tạo mới).
+- [1.5 điểm] Đánh giá retry safety cho Timeline C: Nguy hiểm nếu retry mù quáng, bắt buộc dùng Idempotency Key hoặc API đối soát.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân loại Trạng thái Hoàn tất (Completion Classification) cho Ba Timeline:
+   - Timeline A (Timeout xảy ra trước khi kết nối mạng được thiết lập - Connect Timeout):
+     + Phân loại: CHẮC CHẮN CHƯA HOÀN TẤT (Definitely Not Completed).
+     + Phân tích: Yêu cầu chưa từng rời khỏi máy khách để tới máy chủ nhà cung cấp (chưa hoàn tất TCP/TLS handshake), không có socket nào được kết nối thành công.
+   - Timeline B (Nhà cung cấp đã trả biên lai xác nhận - Provider Receipt Received):
+     + Phân loại: CHẮC CHẮN ĐÃ HOÀN TẤT (Definitely Completed).
+     + Phân tích: Giao dịch đã được tiếp nhận, xử lý và cam kết thành công phía máy chủ, biên lai giao dịch chính thức đã nằm an toàn tại client.
+   - Timeline C (Timeout xảy ra sau khi gửi dữ liệu nhưng chưa nhận được phản hồi - Post-Send Unknown Timeout):
+     + Phân loại: TRẠNG THÁI KHÔNG RÕ RÀNG / LƠ LỬNG (In-Doubt / Indeterminate Completion State).
+     + Phân tích: Yêu cầu đã được gửi qua mạng nhưng timeout đứt kết nối xảy ra trước khi nhận được phản hồi. Không thể biết máy chủ đích đã commit giao dịch vào cơ sở dữ liệu trước khi đứt mạng hay chưa.
+2. Đánh giá Mức độ An toàn khi Thử lại (Retry Safety Evaluation):
+   - Timeline A: AN TOÀN TUYỆT ĐỐI ĐỂ THỬ LẠI (Safe to Retry immediately). Vì nhà cung cấp chưa hề nhận được yêu cầu, việc gửi lại yêu cầu không gây ra bất kỳ tác dụng phụ trùng lặp nào.
+   - Timeline B: TUYỆT ĐỐI KHÔNG THỬ LẠI THỰC THI (Do Not Re-execute / Unsafe to Retry). Nếu cần xác nhận lại dữ liệu, chỉ thực hiện truy vấn đọc trạng thái (`GET /receipts/{id}`) hoặc gửi lại kèm Idempotency Key để nhận lại receipt cũ, cấm tạo transaction mới.
+   - Timeline C: NGUY HIỂM NẾU RETRY MÙ QUÁNG - CHỈ ĐƯỢC RETRY KÈM KHÓA LŨY ĐẲNG (Conditional Retry with Idempotency Key Only). Bắt buộc phải gắn cùng một `Idempotency-Key` duy nhất, hoặc gọi API đối soát kiểm tra trạng thái trước khi quyết định thực thi tiếp nhằm tránh bị trừ tiền hoặc tạo đơn hàng hai lần.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong mạng phân tán, sự cố Timeout không đồng nghĩa với Thất bại (Timeout does not mean Failure). Việc phân biệt chính xác thời điểm xảy ra timeout (trước khi kết nối hay sau khi phát dữ liệu) là nền tảng để thiết lập chiến lược thử lại an toàn, ngăn ngừa triệt để các thảm họa trùng lặp tác vụ ngoài ý muốn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Designing Data-Intensive Applications (Martin Kleppmann) - Unreliable Networks &amp; Idempotent Message Processing Patterns</t>
         </is>
       </c>
     </row>
@@ -1216,10 +1342,30 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách attempt đầu tạo record khỏi các attempt chỉ replay record đó.
-Phân tích theo nguyên lý thiết kế: Tách attempt đầu tạo record khỏi các attempt chỉ replay record đó.</t>
+- [1.0 điểm] Mô tả chính xác lần thực thi đầu tiên: Tạo state effect và lưu kết quả nguyên tử trong cùng một DB transaction trước khi mất mạng.
+- [1.5 điểm] Theo dõi cơ chế xử lý khi Attempt 2 và 3 đến: Kiểm tra khóa K, đối chiếu payload hash và phát hiện trạng thái COMMITTED.
+- [1.5 điểm] Khẳng định hành vi Replay: Trả về kết quả cũ kèm header replay, cam kết tác động thực tế chỉ diễn ra đúng 1 lần duy nhất.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Theo dõi Lần Thực thi Đầu tiên (First Attempt Execution &amp; Atomic Commit):
+   - Khi Attempt 1 đến với ý định nghiệp vụ và `Idempotency-Key: K`:
+   - Hệ thống tra cứu bảng lưu trữ khóa lũy đẳng (`idempotency_store`) trong cơ sở dữ liệu. Không tìm thấy khóa `K`.
+   - Hệ thống mở một DB Transaction nguyên tử (Atomic Unit of Work):
+     + Thực thi tác động nghiệp vụ (State Effect): Tạo bản ghi đơn hàng mới, cập nhật số dư tài khoản.
+     + Ghi nhận bản ghi kết quả vào bảng idempotency:
+       `INSERT INTO idempotency_records (key, status, response_body, payload_hash) VALUES ('K', 'COMMITTED', '{"order_id": "ORD-999", "status": "success"}', 'hash_sha256')`.
+     + Commit Transaction thành công 100% vào cơ sở dữ liệu.
+   - Sự cố xảy ra: Kết nối mạng bị ngắt đột ngột ngay sau khi commit, khiến phản hồi mạng (HTTP 200) bị mất trên đường truyền và client không nhận được.
+2. Theo dõi Các Lần Phát lại Tiếp theo (Subsequent Replay Attempts):
+   - Client gặp timeout và gửi lại Attempt 2, sau đó là Attempt 3 với cùng `Idempotency-Key: K` và cùng payload:
+   - Khi Attempt 2 và Attempt 3 đến máy chủ:
+     + Hệ thống kiểm tra `idempotency_store` và tìm thấy ngay khóa `K` với trạng thái `COMMITTED`.
+     + Kiểm tra tính toàn vẹn: Đối chiếu `payload_hash` của request mới với hash đã lưu để bảo đảm cùng ý định nghiệp vụ.
+     + Cơ chế Phát lại (Idempotent Replay): Hệ thống TUYỆT ĐỐI KHÔNG CHẠY LẠI BẤT KỲ LOGIC NGHIỆP VỤ NÀO (Không tạo đơn hàng mới, không trừ tiền lần 2). Hệ thống đọc trực tiếp `response_body` đã lưu và gửi trả lại cho client kèm header `Idempotent-Replayed: true`.
+     + Kết quả: Cả 3 attempt đều nhận được cùng một kết quả nhất quán, trong khi tác động thực tế ở phía hạ nguồn chỉ xảy ra duy nhất đúng 1 lần (Exactly-Once Effect).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Xử lý lũy đẳng hai pha (Idempotency Record &amp; Replay Pattern) bảo đảm rằng ngay cả khi các gói tin phản hồi bị mất trên đường truyền dẫn đến việc client gửi lại nhiều lần, trạng thái hệ thống vẫn hoàn toàn bất biến sau lần thực thi nguyên tử đầu tiên. Các yêu cầu đến sau chỉ đóng vai trò kích hoạt việc đọc lại kết quả đã lưu mà không bao giờ tái sinh tác dụng phụ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Stripe Engineering Blog - Designing robust and predictable APIs with idempotency: https://stripe.com/blog/idempotency và IETF Draft: The Idempotency-Key HTTP Header Field</t>
         </is>
       </c>
     </row>
@@ -1298,10 +1444,26 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Xác minh authority và business identifier trước khi gộp hai request.
-Phân tích theo nguyên lý thiết kế: Xác minh authority và business identifier trước khi gộp hai request.</t>
+- [1.0 điểm] Phân loại chính xác: R1 và R2 cùng intent (hoàn 100%), R3 là intent khác biệt (hoàn 20%), R4 là intent chưa xác định.
+- [1.5 điểm] Thiết kế khóa định danh Canonical Business Key gộp R1 và R2 chống trùng lặp hoàn tiền, và cấp key riêng cho R3.
+- [1.5 điểm] Xử lý an toàn cho R4: Từ chối tiếp nhận (HTTP 422) do ý định mơ hồ và yêu cầu client bổ sung tham chiếu rõ ràng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân loại Bốn Yêu cầu R1 - R4 theo Ý định Nghiệp vụ (Business Intent Classification):
+   - Cặp R1 và R2: CÙNG MỘT Ý ĐỊNH NGHIỆP VỤ (SAME INTENT).
+     + Phân tích: Cả hai yêu cầu đều áp dụng trên cùng đơn hàng O7, cùng người ủy quyền hợp pháp (Same Authority), và cùng mục đích hoàn trả 100% toàn bộ giá trị đơn hàng (Full Refund). Sự khác biệt câu chữ giữa 'hoàn tiền toàn bộ' và 'hoàn toàn bộ đơn' chỉ là biến thể ngôn ngữ tự nhiên, bản chất nghiệp vụ hoàn toàn đồng nhất.
+   - Yêu cầu R3: Ý ĐỊNH KHÁC BIỆT HOÀN TOÀN (DIFFERENT INTENT).
+     + Phân tích: R3 yêu cầu 'hoàn tiền 20%' (Partial Refund). Đây là một hành động tài chính với số tiền hoàn toàn khác biệt so với việc hoàn tiền toàn bộ 100% của R1/R2.
+   - Yêu cầu R4: Ý ĐỊNH MƠ HỒ / CHƯA XÁC ĐỊNH (AMBIGUOUS / UNCONFIRMED INTENT).
+     + Phân tích: R4 chỉ ghi 'hoàn tiền như cũ' nhưng không có bất kỳ ý định hoặc giao dịch nào trước đó đã được hệ thống xác nhận thành công. Không thể tự suy diễn R4 thuộc nhóm toàn bộ hay một phần mà không có căn cứ đối soát.
+2. Thiết kế Cách Sử dụng Identity và Quản lý Khóa Lũy đẳng:
+   - Quy tắc Ánh xạ Khóa Định danh (Idempotency Key Synthesis):
+     + Đối với R1 và R2: Chuẩn hóa ý định thành một Khóa Định danh Doanh nghiệp Duy nhất (Canonical Business Key): `idempotency:order:O7:refund_full`. Khi R1 được xử lý, khóa được ghi nhận. Khi R2 đến, hệ thống nhận diện cùng Intent Key và trả về kết quả replay của R1 mà không thực hiện hoàn tiền lần 2.
+     + Đối với R3: Cấp phát một Khóa Định danh riêng biệt: `idempotency:order:O7:refund_partial_20`. Cho phép thực thi độc lập (hoặc từ chối hợp lệ nếu đơn hàng đã được R1 hoàn tất 100%).
+     + Đối với R4: BẮT BUỘC TỪ CHỐI TIẾP NHẬN (Reject with HTTP 422 Unprocessable Entity). Yêu cầu client cung cấp mã giao dịch tham chiếu rõ ràng (`referenced_intent_id`) hoặc số tiền cụ thể trước khi cấp phát Identity.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Xử lý ngôn ngữ tự nhiên trong các hệ thống Agent giao dịch đòi hỏi phải phân tách giữa lớp ngữ nghĩa văn bản và lớp định danh nghiệp vụ. Bằng việc chuẩn hóa các văn bản có cùng ý nghĩa thành một khóa định danh doanh nghiệp duy nhất và từ chối các câu lệnh mơ hồ, hệ thống bảo vệ toàn vẹn sổ cái tài chính và ngăn ngừa thất thoát kinh tế.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Enterprise Integration Patterns - Canonical Data Model &amp; Martin Fowler - Event Sourcing and Intent-based APIs</t>
         </is>
       </c>
     </row>
@@ -1380,10 +1542,29 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Phân biệt record đã commit với call đã gửi nhưng chưa được journal ghi nhận.
-Phân tích theo nguyên lý thiết kế: Phân biệt record đã commit với call đã gửi nhưng chưa được journal ghi nhận.</t>
+- [1.0 điểm] Phân định chính xác: Phần đã ghi là bước bắt đầu gọi Tool T; phần chưa ghi là kết quả trả về và bước hoàn tất.
+- [1.5 điểm] Phân tích tác động bên ngoài: Provider có thể đã hoàn tất hành động trong thực tế trước khi client crash.
+- [1.5 điểm] Thiết kế quy trình phục hồi đúng đắn: Cấm gọi lại ngay, thực hiện truy vấn đối soát qua Idempotency Key trước khi commit bù.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Theo dõi Phần Việc Đã ghi và Chưa ghi trong Sổ Nhật ký (Journal Logging State):
+   - Phần việc Đã ghi vào Nhật ký (Committed Journal Record):
+     + Bản ghi bắt đầu gọi công cụ: `JOURNAL_RECORD { event: 'TOOL_INVOCATION_START', tool_name: 'T', idempotency_key: 'IDEM-T-777', timestamp: '...' }` đã được ghi đĩa bền vững trước khi phát request mạng.
+   - Phần việc Chưa ghi vào Nhật ký (Uncommitted / Missing Record):
+     + Bản ghi hoàn tất: `TOOL_INVOCATION_SUCCESS` kèm kết quả trả về của Provider CHƯA ĐƯỢC COMMIT vào nhật ký đĩa cứng do tiến trình bị crash đột ngột ở khoảng cách giữa thời điểm nhận phản hồi mạng và thao tác ghi đĩa.
+2. Theo dõi Tác động Bên ngoài và Quy trình Đối soát Phục hồi (External Effect Reconciliation):
+   - Đánh giá Tác động Bên ngoài (External Effect):
+     Nhà cung cấp bên ngoài (External Provider) có thể ĐÃ THỰC THI THÀNH CÔNG tác vụ (ví dụ: đã gửi tin nhắn SMS, đã tạo bản ghi trên Salesforce, hoặc đã trừ tiền thẻ tín dụng).
+   - Quy trình Phục hồi sau Khởi động lại (Crash Recovery Protocol):
+     + Bước 1: Khi tiến trình khởi động lại, công cụ phục hồi đọc Journal và phát hiện tác vụ Tool T đang ở trạng thái treo (`IN_PROGRESS / PENDING`).
+     + Bước 2 (Nguyên tắc Cốt tử): TUYỆT ĐỐI KHÔNG GỌI LẠI TOOL T NGAY LẬP TỨC vì sẽ gây trùng lặp tác động bên ngoài (Double External Effect).
+     + Bước 3 (Thực hiện Truy vấn Đối soát): Gửi một yêu cầu kiểm tra trạng thái (Status Check / Reconciliation Query) tới Provider sử dụng `idempotency_key: 'IDEM-T-777'`.
+     + Bước 4 (Xử lý Kết quả Đối soát):
+       * Nếu Provider xác nhận tác vụ ĐÃ HOÀN TẤT: Kéo kết quả về, ghi bù bản ghi `TOOL_INVOCATION_SUCCESS` vào Journal và cho phép workflow tiếp tục bước sau.
+       * Nếu Provider xác nhận CHƯA NHẬN ĐƯỢC yêu cầu: Thực hiện gọi lại Tool T an toàn với cùng khóa `idempotency_key`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Vấn đề crash giữa chừng (Crash-Fault Tolerance) là thách thức kinh điển trong kiến trúc giao tác phân tán. Quy trình ghi nhật ký trước (Write-Ahead Logging) kết hợp với cơ chế đối soát trạng thái qua khóa lũy đẳng bảo đảm rằng hệ thống luôn có thể khôi phục trạng thái nhất quán và không bao giờ thực hiện lặp lại một hành động đã diễn ra trong thế giới thực.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Database Recovery Techniques - Write-Ahead Logging (WAL) &amp; Temporal.io Architecture - Durable Execution and Crash Recovery</t>
         </is>
       </c>
     </row>
